--- a/data/boot_true_estimates.xlsx
+++ b/data/boot_true_estimates.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E7D4FF-1429-2145-9920-3B698E4B3CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -239,9 +247,6 @@
     <t>2022-06-21.TN.Quercus montana</t>
   </si>
   <si>
-    <t>2022-06-21.TN.Ulmus americana</t>
-  </si>
-  <si>
     <t>2022-07-26.TN.Acer saccharum</t>
   </si>
   <si>
@@ -272,9 +277,6 @@
     <t>2022-07-26.TN.Quercus montana</t>
   </si>
   <si>
-    <t>2022-07-26.TN.Ulmus americana</t>
-  </si>
-  <si>
     <t>2023-05-17.TN.Acer saccharum</t>
   </si>
   <si>
@@ -323,9 +325,6 @@
     <t>2023-06-13.TN.Quercus montana</t>
   </si>
   <si>
-    <t>2023-06-13.TN.Ulmus americana</t>
-  </si>
-  <si>
     <t>2023-07-23.TN.Acer saccharum</t>
   </si>
   <si>
@@ -356,9 +355,6 @@
     <t>2023-07-23.TN.Quercus montana</t>
   </si>
   <si>
-    <t>2023-07-23.TN.Ulmus americana</t>
-  </si>
-  <si>
     <t>2023-09-11.TN.Acer saccharum</t>
   </si>
   <si>
@@ -389,17 +385,28 @@
     <t>2023-09-11.TN.Quercus montana</t>
   </si>
   <si>
-    <t>2023-09-11.TN.Ulmus americana</t>
+    <t>2022-06-21.TN.Ulmus rubra</t>
+  </si>
+  <si>
+    <t>2022-07-26.TN.Ulmus rubra</t>
+  </si>
+  <si>
+    <t>2023-06-13.TN.Ulmus rubra</t>
+  </si>
+  <si>
+    <t>2023-07-23.TN.Ulmus rubra</t>
+  </si>
+  <si>
+    <t>2023-09-11.TN.Ulmus rubra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -411,7 +418,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -429,16 +436,327 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -452,1044 +770,1044 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="n">
-        <v>46.20253164556962</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>46.202531645569621</v>
+      </c>
+      <c r="D2">
         <v>51.648166188566215</v>
       </c>
-      <c r="E2" t="n">
-        <v>56.4637999978635</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2">
+        <v>56.463799997863497</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
-      <c r="C3" t="n">
-        <v>44.72151898734177</v>
-      </c>
-      <c r="D3" t="n">
-        <v>52.17974328904121</v>
-      </c>
-      <c r="E3" t="n">
-        <v>59.0675747576909</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>44.721518987341767</v>
+      </c>
+      <c r="D3">
+        <v>52.179743289041213</v>
+      </c>
+      <c r="E3">
+        <v>59.067574757690899</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>44.22784810126582</v>
       </c>
-      <c r="D4" t="n">
-        <v>51.83382233398964</v>
-      </c>
-      <c r="E4" t="n">
-        <v>58.7838327595854</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="D4">
+        <v>51.833822333989637</v>
+      </c>
+      <c r="E4">
+        <v>58.783832759585401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>42.253164556962034</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>51.986472215820825</v>
       </c>
-      <c r="E5" t="n">
-        <v>60.45683113111615</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5">
+        <v>60.456831131116147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>43.24050632911392</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>52.3364194503514</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>60.647316260019686</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>43.24050632911392</v>
       </c>
-      <c r="D7" t="n">
-        <v>50.71995220009397</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7">
+        <v>50.719952200093971</v>
+      </c>
+      <c r="E7">
         <v>57.288825551263436</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
-      <c r="C8" t="n">
-        <v>44.22784810126581</v>
-      </c>
-      <c r="D8" t="n">
-        <v>50.94784947390083</v>
-      </c>
-      <c r="E8" t="n">
-        <v>56.83588454870685</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8">
+        <v>44.227848101265813</v>
+      </c>
+      <c r="D8">
+        <v>50.947849473900831</v>
+      </c>
+      <c r="E8">
+        <v>56.835884548706851</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>42.25316455696202</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>51.54435689250144</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>60.110186178783565</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>73</v>
       </c>
-      <c r="C10" t="n">
-        <v>46.20253164556962</v>
-      </c>
-      <c r="D10" t="n">
-        <v>53.94518942770823</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="C10">
+        <v>46.202531645569621</v>
+      </c>
+      <c r="D10">
+        <v>53.945189427708229</v>
+      </c>
+      <c r="E10">
         <v>61.028632541893636</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>43.734177215189874</v>
       </c>
-      <c r="D11" t="n">
-        <v>53.49522120070643</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11">
+        <v>53.495221200706432</v>
+      </c>
+      <c r="E11">
         <v>62.473313928592496</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="n">
-        <v>40.27848101265823</v>
-      </c>
-      <c r="D12" t="n">
-        <v>48.91752596526658</v>
-      </c>
-      <c r="E12" t="n">
+        <v>121</v>
+      </c>
+      <c r="C12">
+        <v>40.278481012658233</v>
+      </c>
+      <c r="D12">
+        <v>48.917525965266577</v>
+      </c>
+      <c r="E12">
         <v>56.847179265133576</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="n">
-        <v>45.70886075949367</v>
-      </c>
-      <c r="D13" t="n">
-        <v>52.39350208074743</v>
-      </c>
-      <c r="E13" t="n">
+        <v>75</v>
+      </c>
+      <c r="C13">
+        <v>45.708860759493668</v>
+      </c>
+      <c r="D13">
+        <v>52.393502080747432</v>
+      </c>
+      <c r="E13">
         <v>58.401689716758206</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="n">
-        <v>47.68354430379746</v>
-      </c>
-      <c r="D14" t="n">
+        <v>76</v>
+      </c>
+      <c r="C14">
+        <v>47.683544303797461</v>
+      </c>
+      <c r="D14">
         <v>53.095117192125024</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>57.639361536965566</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="n">
-        <v>47.68354430379747</v>
-      </c>
-      <c r="D15" t="n">
-        <v>52.71850838709379</v>
-      </c>
-      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="C15">
+        <v>47.683544303797468</v>
+      </c>
+      <c r="D15">
+        <v>52.718508387093792</v>
+      </c>
+      <c r="E15">
         <v>57.25784602703947</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="n">
-        <v>46.69620253164556</v>
-      </c>
-      <c r="D16" t="n">
-        <v>53.6249423329707</v>
-      </c>
-      <c r="E16" t="n">
-        <v>59.71336299333782</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>78</v>
+      </c>
+      <c r="C16">
+        <v>46.696202531645561</v>
+      </c>
+      <c r="D16">
+        <v>53.624942332970697</v>
+      </c>
+      <c r="E16">
+        <v>59.713362993337817</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="n">
+        <v>79</v>
+      </c>
+      <c r="C17">
         <v>45.70886075949366</v>
       </c>
-      <c r="D17" t="n">
-        <v>54.32446387025858</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17">
+        <v>54.324463870258583</v>
+      </c>
+      <c r="E17">
         <v>61.82285651151799</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18">
         <v>43.734177215189874</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>52.498396004243936</v>
       </c>
-      <c r="E18" t="n">
-        <v>60.02002890878481</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="E18">
+        <v>60.020028908784809</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="n">
-        <v>48.17721518987342</v>
-      </c>
-      <c r="D19" t="n">
-        <v>51.82702745765293</v>
-      </c>
-      <c r="E19" t="n">
-        <v>54.96250235517875</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>81</v>
+      </c>
+      <c r="C19">
+        <v>48.177215189873422</v>
+      </c>
+      <c r="D19">
+        <v>51.827027457652932</v>
+      </c>
+      <c r="E19">
+        <v>54.962502355178749</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="n">
-        <v>46.20253164556963</v>
-      </c>
-      <c r="D20" t="n">
+        <v>82</v>
+      </c>
+      <c r="C20">
+        <v>46.202531645569628</v>
+      </c>
+      <c r="D20">
         <v>52.012520603904136</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>57.360435652604664</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="n">
+        <v>83</v>
+      </c>
+      <c r="C21">
         <v>44.22784810126582</v>
       </c>
-      <c r="D21" t="n">
-        <v>55.84154779622993</v>
-      </c>
-      <c r="E21" t="n">
-        <v>66.20310130724316</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="D21">
+        <v>55.841547796229932</v>
+      </c>
+      <c r="E21">
+        <v>66.203101307243159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="n">
+        <v>84</v>
+      </c>
+      <c r="C22">
         <v>44.721518987341774</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>52.639494199853516</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>59.687139960935454</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="n">
-        <v>47.18987341772152</v>
-      </c>
-      <c r="D23" t="n">
+        <v>122</v>
+      </c>
+      <c r="C23">
+        <v>47.189873417721522</v>
+      </c>
+      <c r="D23">
         <v>53.462418660824824</v>
       </c>
-      <c r="E23" t="n">
-        <v>59.46166414619346</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="E23">
+        <v>59.461664146193463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="n">
+        <v>85</v>
+      </c>
+      <c r="C24">
         <v>41.265822784810126</v>
       </c>
-      <c r="D24" t="n">
-        <v>49.03855036426672</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24">
+        <v>49.038550364266719</v>
+      </c>
+      <c r="E24">
         <v>55.878570906727546</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="n">
-        <v>42.25316455696203</v>
-      </c>
-      <c r="D25" t="n">
+        <v>86</v>
+      </c>
+      <c r="C25">
+        <v>42.253164556962027</v>
+      </c>
+      <c r="D25">
         <v>48.503518239612454</v>
       </c>
-      <c r="E25" t="n">
-        <v>54.17278291418915</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="E25">
+        <v>54.172782914189149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="n">
+        <v>87</v>
+      </c>
+      <c r="C26">
         <v>40.27848101265824</v>
       </c>
-      <c r="D26" t="n">
-        <v>49.69669061146453</v>
-      </c>
-      <c r="E26" t="n">
-        <v>58.19044109621595</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="D26">
+        <v>49.696690611464533</v>
+      </c>
+      <c r="E26">
+        <v>58.190441096215949</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="n">
-        <v>45.21518987341772</v>
-      </c>
-      <c r="D27" t="n">
-        <v>48.76115032305768</v>
-      </c>
-      <c r="E27" t="n">
+        <v>88</v>
+      </c>
+      <c r="C27">
+        <v>45.215189873417721</v>
+      </c>
+      <c r="D27">
+        <v>48.761150323057677</v>
+      </c>
+      <c r="E27">
         <v>52.054517836817006</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="n">
+        <v>89</v>
+      </c>
+      <c r="C28">
         <v>43.240506329113934</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>48.377337918957146</v>
       </c>
-      <c r="E28" t="n">
-        <v>52.80826444252113</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="E28">
+        <v>52.808264442521129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="n">
+        <v>90</v>
+      </c>
+      <c r="C29">
         <v>40.77215189873418</v>
       </c>
-      <c r="D29" t="n">
-        <v>49.28535309345874</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29">
+        <v>49.285353093458738</v>
+      </c>
+      <c r="E29">
         <v>56.938276010598116</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="n">
-        <v>43.24050632911393</v>
-      </c>
-      <c r="D30" t="n">
+        <v>91</v>
+      </c>
+      <c r="C30">
+        <v>43.240506329113927</v>
+      </c>
+      <c r="D30">
         <v>49.191603962405914</v>
       </c>
-      <c r="E30" t="n">
-        <v>54.63828111969349</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="E30">
+        <v>54.638281119693488</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="n">
+        <v>92</v>
+      </c>
+      <c r="C31">
         <v>42.25316455696202</v>
       </c>
-      <c r="D31" t="n">
-        <v>50.4246203502223</v>
-      </c>
-      <c r="E31" t="n">
-        <v>57.56023374180854</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="D31">
+        <v>50.424620350222298</v>
+      </c>
+      <c r="E31">
+        <v>57.560233741808538</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="n">
-        <v>40.77215189873419</v>
-      </c>
-      <c r="D32" t="n">
-        <v>46.43369899273208</v>
-      </c>
-      <c r="E32" t="n">
-        <v>51.81359465538202</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>93</v>
+      </c>
+      <c r="C32">
+        <v>40.772151898734187</v>
+      </c>
+      <c r="D32">
+        <v>46.433698992732083</v>
+      </c>
+      <c r="E32">
+        <v>51.813594655382019</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" t="n">
+        <v>94</v>
+      </c>
+      <c r="C33">
         <v>45.708860759493675</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>49.732657297549785</v>
       </c>
-      <c r="E33" t="n">
-        <v>53.12684973965227</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="E33">
+        <v>53.126849739652272</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="n">
-        <v>44.72151898734178</v>
-      </c>
-      <c r="D34" t="n">
-        <v>50.04733927156651</v>
-      </c>
-      <c r="E34" t="n">
+        <v>95</v>
+      </c>
+      <c r="C34">
+        <v>44.721518987341781</v>
+      </c>
+      <c r="D34">
+        <v>50.047339271566507</v>
+      </c>
+      <c r="E34">
         <v>54.992851367885606</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="n">
-        <v>38.79746835443037</v>
-      </c>
-      <c r="D35" t="n">
-        <v>50.39023825324717</v>
-      </c>
-      <c r="E35" t="n">
+        <v>96</v>
+      </c>
+      <c r="C35">
+        <v>38.797468354430372</v>
+      </c>
+      <c r="D35">
+        <v>50.390238253247169</v>
+      </c>
+      <c r="E35">
         <v>60.442998973309784</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="n">
+        <v>97</v>
+      </c>
+      <c r="C36">
         <v>39.784810126582286</v>
       </c>
-      <c r="D36" t="n">
-        <v>45.94962271163231</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="D36">
+        <v>45.949622711632308</v>
+      </c>
+      <c r="E36">
         <v>51.560804988007895</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="n">
+        <v>98</v>
+      </c>
+      <c r="C37">
         <v>44.721518987341774</v>
       </c>
-      <c r="D37" t="n">
-        <v>49.8405770854539</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D37">
+        <v>49.840577085453901</v>
+      </c>
+      <c r="E37">
         <v>55.601543375662715</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" t="n">
-        <v>38.79746835443037</v>
-      </c>
-      <c r="D38" t="n">
-        <v>50.41058798186853</v>
-      </c>
-      <c r="E38" t="n">
-        <v>60.58054995163219</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>99</v>
+      </c>
+      <c r="C38">
+        <v>38.797468354430372</v>
+      </c>
+      <c r="D38">
+        <v>50.410587981868531</v>
+      </c>
+      <c r="E38">
+        <v>60.580549951632193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="n">
-        <v>41.75949367088607</v>
-      </c>
-      <c r="D39" t="n">
-        <v>50.84663198156561</v>
-      </c>
-      <c r="E39" t="n">
-        <v>58.81599861317414</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>100</v>
+      </c>
+      <c r="C39">
+        <v>41.759493670886073</v>
+      </c>
+      <c r="D39">
+        <v>50.846631981565608</v>
+      </c>
+      <c r="E39">
+        <v>58.815998613174138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" t="n">
-        <v>41.26582278481012</v>
-      </c>
-      <c r="D40" t="n">
-        <v>48.78732110402404</v>
-      </c>
-      <c r="E40" t="n">
-        <v>56.36930320731137</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>123</v>
+      </c>
+      <c r="C40">
+        <v>41.265822784810119</v>
+      </c>
+      <c r="D40">
+        <v>48.787321104024038</v>
+      </c>
+      <c r="E40">
+        <v>56.369303207311368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" t="n">
-        <v>43.24050632911393</v>
-      </c>
-      <c r="D41" t="n">
+        <v>101</v>
+      </c>
+      <c r="C41">
+        <v>43.240506329113927</v>
+      </c>
+      <c r="D41">
         <v>49.543979250753246</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>54.852958532119835</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" t="n">
-        <v>44.22784810126583</v>
-      </c>
-      <c r="D42" t="n">
-        <v>50.4443418848738</v>
-      </c>
-      <c r="E42" t="n">
-        <v>55.87070158455012</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>102</v>
+      </c>
+      <c r="C42">
+        <v>44.227848101265828</v>
+      </c>
+      <c r="D42">
+        <v>50.444341884873801</v>
+      </c>
+      <c r="E42">
+        <v>55.870701584550119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" t="n">
-        <v>44.22784810126583</v>
-      </c>
-      <c r="D43" t="n">
-        <v>49.71937116212722</v>
-      </c>
-      <c r="E43" t="n">
-        <v>55.33982098415762</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>103</v>
+      </c>
+      <c r="C43">
+        <v>44.227848101265828</v>
+      </c>
+      <c r="D43">
+        <v>49.719371162127217</v>
+      </c>
+      <c r="E43">
+        <v>55.339820984157619</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" t="n">
-        <v>47.18987341772152</v>
-      </c>
-      <c r="D44" t="n">
-        <v>51.23793550557085</v>
-      </c>
-      <c r="E44" t="n">
+        <v>104</v>
+      </c>
+      <c r="C44">
+        <v>47.189873417721522</v>
+      </c>
+      <c r="D44">
+        <v>51.237935505570853</v>
+      </c>
+      <c r="E44">
         <v>54.873598057170966</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
-      </c>
-      <c r="C45" t="n">
+        <v>105</v>
+      </c>
+      <c r="C45">
         <v>41.75949367088608</v>
       </c>
-      <c r="D45" t="n">
-        <v>51.51491722543851</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45">
+        <v>51.514917225438509</v>
+      </c>
+      <c r="E45">
         <v>60.234423136780215</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" t="n">
-        <v>40.77215189873417</v>
-      </c>
-      <c r="D46" t="n">
+        <v>106</v>
+      </c>
+      <c r="C46">
+        <v>40.772151898734172</v>
+      </c>
+      <c r="D46">
         <v>50.585385175372195</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>59.287285357481046</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
-      </c>
-      <c r="C47" t="n">
-        <v>39.29113924050632</v>
-      </c>
-      <c r="D47" t="n">
-        <v>47.60266445389401</v>
-      </c>
-      <c r="E47" t="n">
-        <v>54.95457029879383</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>107</v>
+      </c>
+      <c r="C47">
+        <v>39.291139240506318</v>
+      </c>
+      <c r="D47">
+        <v>47.602664453894008</v>
+      </c>
+      <c r="E47">
+        <v>54.954570298793833</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" t="n">
-        <v>49.16455696202531</v>
-      </c>
-      <c r="D48" t="n">
+        <v>108</v>
+      </c>
+      <c r="C48">
+        <v>49.164556962025308</v>
+      </c>
+      <c r="D48">
         <v>53.628822778155346</v>
       </c>
-      <c r="E48" t="n">
-        <v>56.97968238347829</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="E48">
+        <v>56.979682383478291</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" t="n">
-        <v>44.72151898734178</v>
-      </c>
-      <c r="D49" t="n">
-        <v>54.3235605908451</v>
-      </c>
-      <c r="E49" t="n">
-        <v>62.46155814079685</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>109</v>
+      </c>
+      <c r="C49">
+        <v>44.721518987341781</v>
+      </c>
+      <c r="D49">
+        <v>54.323560590845098</v>
+      </c>
+      <c r="E49">
+        <v>62.461558140796853</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" t="n">
+        <v>110</v>
+      </c>
+      <c r="C50">
         <v>42.74683544303798</v>
       </c>
-      <c r="D50" t="n">
-        <v>51.46729993640487</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="D50">
+        <v>51.467299936404871</v>
+      </c>
+      <c r="E50">
         <v>59.1780502264413</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" t="n">
+        <v>124</v>
+      </c>
+      <c r="C51">
         <v>43.73417721518986</v>
       </c>
-      <c r="D51" t="n">
-        <v>51.15752255880203</v>
-      </c>
-      <c r="E51" t="n">
-        <v>58.47082726852499</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="D51">
+        <v>51.157522558802029</v>
+      </c>
+      <c r="E51">
+        <v>58.470827268524992</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" t="n">
-        <v>42.25316455696203</v>
-      </c>
-      <c r="D52" t="n">
-        <v>47.36257641492547</v>
-      </c>
-      <c r="E52" t="n">
-        <v>52.87064210016892</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>111</v>
+      </c>
+      <c r="C52">
+        <v>42.253164556962027</v>
+      </c>
+      <c r="D52">
+        <v>47.362576414925471</v>
+      </c>
+      <c r="E52">
+        <v>52.870642100168922</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" t="n">
-        <v>47.68354430379747</v>
-      </c>
-      <c r="D53" t="n">
-        <v>52.43701724325518</v>
-      </c>
-      <c r="E53" t="n">
-        <v>56.76721547368262</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>112</v>
+      </c>
+      <c r="C53">
+        <v>47.683544303797468</v>
+      </c>
+      <c r="D53">
+        <v>52.437017243255177</v>
+      </c>
+      <c r="E53">
+        <v>56.767215473682619</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" t="n">
+        <v>113</v>
+      </c>
+      <c r="C54">
         <v>39.291139240506325</v>
       </c>
-      <c r="D54" t="n">
-        <v>46.62068289817605</v>
-      </c>
-      <c r="E54" t="n">
-        <v>54.47846201083129</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="D54">
+        <v>46.620682898176049</v>
+      </c>
+      <c r="E54">
+        <v>54.478462010831286</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" t="n">
-        <v>47.18987341772152</v>
-      </c>
-      <c r="D55" t="n">
-        <v>51.91512037166782</v>
-      </c>
-      <c r="E55" t="n">
-        <v>56.17737758394149</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>114</v>
+      </c>
+      <c r="C55">
+        <v>47.189873417721522</v>
+      </c>
+      <c r="D55">
+        <v>51.915120371667818</v>
+      </c>
+      <c r="E55">
+        <v>56.177377583941492</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C56" t="n">
-        <v>47.18987341772152</v>
-      </c>
-      <c r="D56" t="n">
-        <v>51.22222503520457</v>
-      </c>
-      <c r="E56" t="n">
+        <v>115</v>
+      </c>
+      <c r="C56">
+        <v>47.189873417721522</v>
+      </c>
+      <c r="D56">
+        <v>51.222225035204573</v>
+      </c>
+      <c r="E56">
         <v>54.682371258256495</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" t="n">
+        <v>116</v>
+      </c>
+      <c r="C57">
         <v>42.253164556962034</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>50.121466136693144</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>56.811357345240275</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
-      </c>
-      <c r="C58" t="n">
+        <v>117</v>
+      </c>
+      <c r="C58">
         <v>25.468354430379748</v>
       </c>
-      <c r="D58" t="n">
-        <v>41.61073435762839</v>
-      </c>
-      <c r="E58" t="n">
-        <v>56.34638453787955</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="D58">
+        <v>41.610734357628388</v>
+      </c>
+      <c r="E58">
+        <v>56.346384537879551</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
-      </c>
-      <c r="C59" t="n">
+        <v>118</v>
+      </c>
+      <c r="C59">
         <v>40.278481012658226</v>
       </c>
-      <c r="D59" t="n">
-        <v>52.32978071876901</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="D59">
+        <v>52.329780718769008</v>
+      </c>
+      <c r="E59">
         <v>62.19721789427301</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" t="n">
+        <v>119</v>
+      </c>
+      <c r="C60">
         <v>43.734177215189874</v>
       </c>
-      <c r="D60" t="n">
-        <v>52.21557786194155</v>
-      </c>
-      <c r="E60" t="n">
-        <v>60.2666136645266</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="D60">
+        <v>52.215577861941547</v>
+      </c>
+      <c r="E60">
+        <v>60.266613664526602</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" t="n">
+        <v>120</v>
+      </c>
+      <c r="C61">
         <v>44.22784810126582</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>50.621212688478764</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>56.310301765558215</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62" t="s">
         <v>125</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>27.936708860759477</v>
       </c>
-      <c r="D62" t="n">
-        <v>47.95261270209358</v>
-      </c>
-      <c r="E62" t="n">
-        <v>67.51833008444808</v>
+      <c r="D62">
+        <v>47.952612702093582</v>
+      </c>
+      <c r="E62">
+        <v>67.518330084448081</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>